--- a/part3_regression_insights/outputs/regression_summary.xlsx
+++ b/part3_regression_insights/outputs/regression_summary.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70F91820-C499-461F-BF8E-9C59465DCCFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11110" yWindow="0" windowWidth="11380" windowHeight="13370" xr2:uid="{1715B296-04F5-4595-9C3F-FD0D3482FBCD}"/>
+    <workbookView xWindow="3220" yWindow="3220" windowWidth="16800" windowHeight="9670" xr2:uid="{1715B296-04F5-4595-9C3F-FD0D3482FBCD}"/>
   </bookViews>
   <sheets>
     <sheet name="model_summary" sheetId="1" r:id="rId1"/>
@@ -143,13 +143,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -501,7 +500,7 @@
     <row r="2" spans="1:6" ht="18">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:6" ht="43.5">
+    <row r="3" spans="1:6" ht="29">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -537,7 +536,7 @@
       <c r="E4">
         <v>2.13</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="3">
         <v>2.4799999999999999E-14</v>
       </c>
     </row>
@@ -557,7 +556,7 @@
       <c r="E5">
         <v>35.68</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="3">
         <v>4.7499999999999999E-94</v>
       </c>
     </row>
@@ -585,7 +584,7 @@
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" t="s">
         <v>15</v>
       </c>
       <c r="C7">

--- a/part3_regression_insights/outputs/regression_summary.xlsx
+++ b/part3_regression_insights/outputs/regression_summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mitali Kalburgi\OneDrive\Desktop\Bitsom Notes\Assignments\Final Capstone Project\part3_regression_insights\part3_regression_insights\outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70F91820-C499-461F-BF8E-9C59465DCCFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{923BACE1-3578-40C1-A0A4-BED727A33FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3220" yWindow="3220" windowWidth="16800" windowHeight="9670" xr2:uid="{1715B296-04F5-4595-9C3F-FD0D3482FBCD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{1715B296-04F5-4595-9C3F-FD0D3482FBCD}"/>
   </bookViews>
   <sheets>
     <sheet name="model_summary" sheetId="1" r:id="rId1"/>
@@ -109,7 +109,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -122,16 +122,27 @@
       <sz val="14"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF365F91"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -139,24 +150,197 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="7">
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF365F91"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -172,16 +356,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{9956A062-E107-4C77-A430-F8226F3B8BC8}" name="Table2" displayName="Table2" ref="A3:F8" insertRowShift="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{9956A062-E107-4C77-A430-F8226F3B8BC8}" name="Table2" displayName="Table2" ref="A3:F8" insertRowShift="1" totalsRowShown="0" headerRowDxfId="6">
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{EAFC4AFE-57CA-46B4-A4BD-1A988363E7FF}" name="Model Name" dataDxfId="0"/>
-    <tableColumn id="2" xr3:uid="{5F92C6FB-6930-4B1C-8DD9-846C413127C7}" name="Independent Variable(s)"/>
-    <tableColumn id="3" xr3:uid="{120D2C81-C3BC-4558-8B9B-EA30F09039CD}" name="R-squared"/>
-    <tableColumn id="4" xr3:uid="{AAE6506F-C926-464C-A0AE-68CE4FD8DD75}" name="Significant?"/>
-    <tableColumn id="5" xr3:uid="{9EC6472D-0988-4CA7-9C54-343640B24CC8}" name="Coefficient (key variable)"/>
-    <tableColumn id="6" xr3:uid="{DF9595E9-7321-48EE-B1BA-5D9E47AEE229}" name="P-value (key variable)"/>
+    <tableColumn id="1" xr3:uid="{EAFC4AFE-57CA-46B4-A4BD-1A988363E7FF}" name="Model Name" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{5F92C6FB-6930-4B1C-8DD9-846C413127C7}" name="Independent Variable(s)" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{120D2C81-C3BC-4558-8B9B-EA30F09039CD}" name="R-squared" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{AAE6506F-C926-464C-A0AE-68CE4FD8DD75}" name="Significant?" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{9EC6472D-0988-4CA7-9C54-343640B24CC8}" name="Coefficient (key variable)" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{DF9595E9-7321-48EE-B1BA-5D9E47AEE229}" name="P-value (key variable)" dataDxfId="0"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -500,17 +684,17 @@
     <row r="2" spans="1:6" ht="18">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:6" ht="29">
-      <c r="A3" t="s">
+    <row r="3" spans="1:6" ht="28">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="2" t="s">
@@ -521,102 +705,102 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="29">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="4">
         <v>0.16700000000000001</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="4">
         <v>2.13</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="5">
         <v>2.4799999999999999E-14</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="23" customHeight="1">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="4">
         <v>0.73599999999999999</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="4">
         <v>35.68</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="5">
         <v>4.7499999999999999E-94</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="29">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="4">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="4">
         <v>-138730.45000000001</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="4">
         <v>0.104</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="43.5">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="4">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="4">
         <v>2217.83</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="4">
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="100.5" customHeight="1">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="4">
         <v>0.82099999999999995</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>22</v>
       </c>
     </row>
